--- a/forms/trg/Formulir_TRG_govmo-soc.xlsx
+++ b/forms/trg/Formulir_TRG_govmo-soc.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. Dr. Nurlinah, M.Si</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Department of Government Science, Hasanuddin University</t>
@@ -959,7 +963,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -1004,7 +1008,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1049,7 +1053,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1090,7 +1094,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1127,7 +1131,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1168,7 +1172,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1213,7 +1217,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1254,7 +1258,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1291,7 +1295,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1299,7 +1303,11 @@
           <t>Department of Government Science, Hasanuddin University</t>
         </is>
       </c>
-      <c r="E14" s="11" t="n"/>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Welcome to the Government Modernization and Social Change Research Group (GMSC), a research team dedicated to studying governance modernization and social transformation.</t>
+        </is>
+      </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
